--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>24/08 13:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F13" t="n">
+        <v>3.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F15" t="n">
+        <v>2.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>19/08 23:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>25</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>20/08 00:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>20</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/08 01:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>26/08 00:15</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1.75</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>60</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45888.07359889495</v>
+        <v>45888.07359890046</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+1,47%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45888.07359890046</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico L</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atletico Lanus – Central CordobaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+1,47%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45888.07359889495</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45888.13342489731</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21-2- se qualifie | Brann-Berg</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brann-Bergen – AEK LarnacaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21/08 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45888.13342489731</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>50</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45888.13342489731</v>
+        <v>45888.13342489583</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>21/08 17:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.65</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45888.13342489731</v>
+        <v>45888.13342489583</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 8.51er set | Petra Mart</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Petra Martic – Xiyu WangWTA - US Open, Qualifications</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20/08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,92%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45888.18489611793</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>20/08 15:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45888.18489611793</v>
+        <v>45888.18489612269</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | Wehen Wies</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden – Bayern MunichAllemagne. Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+6,92%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45888.22326076655</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Riga FCLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+3,07%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45888.22326076655</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>55</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45888.22326076655</v>
+        <v>45888.22326076389</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,367 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45888.22326076655</v>
+        <v>45888.22326076389</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Mushuc Run</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mushuc Runa – Independiente Del ValleInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+45,6%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Breidablik</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Breidablik – SS VirtusLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+38,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+29,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 9.5 - tirs2e équipe | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – Atletico NacionalInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>67,5%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+28,3%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 10.5 - tir cadré | Juventude </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Juventude RS – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20/08 22:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+18,3%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 10.5 - tir cadré | Ferencvaro</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ferencvaros – Qarabag AgdamEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 18.5 - tirs1re équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Racing Club – Penarol de MontevideoInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+13,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45888.27341634843</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Club BrugesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+6,01%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45888.27341634843</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2.95</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>65</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.85</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="36">
@@ -1975,10 +1967,8 @@
           <t>20/08 22:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F36" t="n">
+        <v>3.6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1991,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="37">
@@ -2020,10 +2010,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2036,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="38">
@@ -2065,10 +2053,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2081,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
       </c>
     </row>
     <row r="39">
@@ -2110,10 +2096,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3.9</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2126,7 +2110,187 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45888.27341634843</v>
+        <v>45888.27341635417</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 25.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Club BrugesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+40,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45888.30649998668</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 15.5 - tirs1re équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+29,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45888.30649998668</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 1 - aces | Botic Van </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp – Matteo ArnaldiATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19/08 21:10</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+7,39%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45888.30649998668</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 2 - aces | Sebastian </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sebastian Baez – Pablo Carreno-BustaATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/08 20:20</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+6,52%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45888.30649998668</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.9</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45888.30649998668</v>
+        <v>45888.30649998842</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.62</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45888.30649998668</v>
+        <v>45888.30649998842</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>19/08 21:10</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45888.30649998668</v>
+        <v>45888.30649998842</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>19/08 20:20</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F43" t="n">
+        <v>1.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,277 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45888.30649998668</v>
+        <v>45888.30649998842</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Crystal Palace – FredrikstadLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+40,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45888.35384504312</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 16.5 - tirs1re équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+23,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45888.35384504312</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spezia – C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Spezia – CarrareseSerie B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+9,64%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45888.35384504312</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 27.5 - tirs | Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt – Sturm GrazLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+8,89%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45888.35384504312</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Stefanos T</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas – Yunchaokete BuATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19/08 22:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+8,56%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45888.35384504312</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Darwin Bla</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Darwin Blanch – Alexandre MullerATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19/08 18:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+6,50%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45888.35384504312</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>65</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>50</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
       </c>
     </row>
     <row r="47">
@@ -2446,10 +2440,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F47" t="n">
+        <v>1.78</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
       </c>
     </row>
     <row r="48">
@@ -2491,10 +2483,8 @@
           <t>19/08 22:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2507,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
       </c>
     </row>
     <row r="49">
@@ -2536,10 +2526,8 @@
           <t>19/08 18:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2552,7 +2540,187 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45888.35384504312</v>
+        <v>45888.35384504629</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 22.5 - tirs | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – Atletico NacionalInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+27,9%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45888.39142061891</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 6.5 - tir cadré1re équipe | Ferencvaro</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ferencvaros – Qarabag AgdamEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45888.39142061891</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 8.5 - tir cadré1re équipe | Real Madri</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,36%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45888.39142061891</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Hamad Medj</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hamad Medjedovic – Jacob FearnleyATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19/08 20:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+2,91%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45888.39142061891</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.65</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45888.39142061891</v>
+        <v>45888.39142061343</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F51" t="n">
+        <v>3.7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45888.39142061891</v>
+        <v>45888.39142061343</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>3</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45888.39142061891</v>
+        <v>45888.39142061343</v>
       </c>
     </row>
     <row r="53">
@@ -2704,10 +2698,8 @@
           <t>19/08 20:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F53" t="n">
+        <v>1.3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2720,7 +2712,232 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45888.39142061891</v>
+        <v>45888.39142061343</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Club BrugesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+23,2%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45888.43321073652</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 21.5 - tirs | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45888.43321073652</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | H 2 (+6.5) | Blockx – J</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Blockx – Jo Reis Da SilvaUS Open 2025 - Hommes</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>H 2 (+6.5)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/08 23:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+5,59%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45888.43321073652</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 29.5 - tirs | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – Atletico NacionalInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+5,18%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45888.43321073652</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | River Plat</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>River Plate (ARG) – Libertad AsuncionInternational. Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+4,83%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45888.43321073652</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45888.43321073652</v>
+        <v>45888.43321074074</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3.1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45888.43321073652</v>
+        <v>45888.43321074074</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>19/08 23:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F56" t="n">
+        <v>1.6</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45888.43321073652</v>
+        <v>45888.43321074074</v>
       </c>
     </row>
     <row r="57">
@@ -2876,10 +2870,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3.2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2892,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45888.43321073652</v>
+        <v>45888.43321074074</v>
       </c>
     </row>
     <row r="58">
@@ -2921,23 +2913,111 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+4,83%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45888.43321074074</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Lorenzo So</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lorenzo Sonego – Stefan DostanicATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19/08 23:40</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>6.50</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>+4,83%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>45888.43321073652</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45888.47137128194</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 21.5 - tirs | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>38,4%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,46%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45888.47137128194</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>19/08 23:40</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F59" t="n">
+        <v>6.5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45888.47137128194</v>
+        <v>45888.47137128472</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F60" t="n">
+        <v>2.75</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,187 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45888.47137128194</v>
+        <v>45888.47137128472</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 2 (−3.5) | Knattspyrn</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Knattspyrnufelagid Kria – KA AsvellirIceland - 4. deild</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>H 2 (−3.5)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19/08 19:15</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+13,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45888.53065795034</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 2 (−3.5) | Holstin Dy</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Holstin Dynamo – Huima/UrhoFinland - Kolmonen</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>H 2 (−3.5)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20/08 16:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45888.53065795034</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Brann – AE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brann – AEK LarnacaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>21/08 17:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+7,48%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45888.53065795034</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Juventude </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Juventude RS – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/08 22:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>54,3%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+5,86%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45888.53065795034</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>19/08 19:15</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45888.53065795034</v>
+        <v>45888.53065795139</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>20/08 16:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3.8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45888.53065795034</v>
+        <v>45888.53065795139</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>21/08 17:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.65</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45888.53065795034</v>
+        <v>45888.53065795139</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>20/08 22:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.95</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,142 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45888.53065795034</v>
+        <v>45888.53065795139</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tirs2e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Racing Club – Penarol de MontevideoInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+49,9%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45888.56421013009</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 15.5 - tirs1re équipe | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – Atletico NacionalInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+6,25%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45888.56421013009</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 21-2- se qualifie | Huracan – </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Huracan – Once CaldasInternational. Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19/08 22:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+5,57%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45888.56421013009</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F65" t="n">
+        <v>3.1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45888.56421013009</v>
+        <v>45888.56421012731</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45888.56421013009</v>
+        <v>45888.56421012731</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>19/08 22:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F67" t="n">
+        <v>2.1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,277 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45888.56421013009</v>
+        <v>45888.56421012731</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set1er participant | Lorenzo So</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lorenzo Sonego – Stefan Dostanic385076e7 ATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19/08 23:40</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+14,8%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45888.5987470153</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Racing Club – Penarol de MontevideoInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+13,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45888.5987470153</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 8.5 - tir cadré1re équipe | Real Madri</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaLaLiga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45888.5987470153</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20/08 02:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45888.5987470153</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 4.5 - break | Mariano Na</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mariano Navone – Marcos Giron385076e7 ATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - break</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19/08 20:20</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+6,94%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45888.5987470153</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré2e équipe | Mushuc Run</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mushuc Runa – Independiente Del ValleInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+6,38%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45888.5987470153</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>19/08 23:40</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="F68" t="n">
+        <v>7.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
       </c>
     </row>
     <row r="69">
@@ -3388,10 +3386,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F69" t="n">
+        <v>3.7</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
       </c>
     </row>
     <row r="70">
@@ -3433,10 +3429,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>3</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3449,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
       </c>
     </row>
     <row r="71">
@@ -3478,10 +3472,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3494,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
       </c>
     </row>
     <row r="72">
@@ -3523,10 +3515,8 @@
           <t>19/08 20:20</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3539,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
       </c>
     </row>
     <row r="73">
@@ -3568,10 +3558,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3584,7 +3572,322 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45888.5987470153</v>
+        <v>45888.59874701389</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | SC Kolin –</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SC Kolin – HC Slavia PragueInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>19/08 15:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+33,6%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | HC Zubr Pr</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HC Zubr Prerov – HC Frydek MistekInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19/08 15:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+26,8%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Hockey | Pas de buts | HC Sparta </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HC Sparta Prague – HC Motor Ceske BudejoviceInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19/08 15:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 9.5 - tir cadré | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FC Bâle – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+15,1%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs2e équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fluminense – America de CaliInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+9,71%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Racing Club – Penarol de MontevideoInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+9,68%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45888.6416151394</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Instituto AC CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+8,43%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45888.6416151394</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,10 +3601,8 @@
           <t>19/08 15:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>70</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="75">
@@ -3646,10 +3644,8 @@
           <t>19/08 15:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>65</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="76">
@@ -3691,10 +3687,8 @@
           <t>19/08 15:30</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>65</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3707,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="77">
@@ -3736,10 +3730,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F77" t="n">
+        <v>2.6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3752,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="78">
@@ -3781,10 +3773,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.7</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3797,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="79">
@@ -3826,10 +3816,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F79" t="n">
+        <v>3.1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3842,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
       </c>
     </row>
     <row r="80">
@@ -3871,10 +3859,8 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>55</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3887,7 +3873,187 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45888.6416151394</v>
+        <v>45888.64161513889</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | KH Zaglebi</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KH Zaglebie Sosnowiec – JKH GKS JastrzębieInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19/08 16:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+57,4%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45888.68596438483</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey | Pas de buts | Linz – Bil</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Linz – Bili Tygri LiberecInternational - Club Friendly Games</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19/08 16:30</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,90%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+23,5%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45888.68596438483</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 9.5 - tir cadré | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FC Bâle – FC CopenhagueLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45888.68596438483</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Real Madri</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaLaLiga</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+5,31%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45888.68596438483</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,10 +3902,8 @@
           <t>19/08 16:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>90</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45888.68596438483</v>
+        <v>45888.68596438658</v>
       </c>
     </row>
     <row r="82">
@@ -3947,10 +3945,8 @@
           <t>19/08 16:30</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>65</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3963,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45888.68596438483</v>
+        <v>45888.68596438658</v>
       </c>
     </row>
     <row r="83">
@@ -3992,10 +3988,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F83" t="n">
+        <v>2.55</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4008,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45888.68596438483</v>
+        <v>45888.68596438658</v>
       </c>
     </row>
     <row r="84">
@@ -4037,10 +4031,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F84" t="n">
+        <v>2.5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4053,7 +4045,52 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45888.68596438483</v>
+        <v>45888.68596438658</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 20.5 - tirs1re équipe | Real Madri</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Plus que 20.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+7,02%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45888.72190754786</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4074,10 +4074,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F85" t="n">
+        <v>2.9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4090,7 +4088,97 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45888.72190754786</v>
+        <v>45888.7219075463</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Korsnas IF</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Korsnas IF FK – Hammarby IFSweden - Svenska Cupen</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20/08 16:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45888.77063883623</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 25.5 - tirs | Velez Sars</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield – Fortaleza CE385076e7 International - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Plus que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>19/08 22:00</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+3,44%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45888.77063883623</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,10 +4117,8 @@
           <t>20/08 16:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>25</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4133,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45888.77063883623</v>
+        <v>45888.77063883102</v>
       </c>
     </row>
     <row r="87">
@@ -4162,10 +4160,8 @@
           <t>19/08 22:00</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F87" t="n">
+        <v>2.65</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4178,7 +4174,52 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45888.77063883623</v>
+        <v>45888.77063883102</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(16:0)P | Belgique –</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Belgique – FranceBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>X(16:0)P</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>28/08 15:00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+5,94%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45888.80381287629</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4203,10 +4203,8 @@
           <t>28/08 15:00</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
+      <c r="F88" t="n">
+        <v>18.5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4219,7 +4217,187 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45888.80381287629</v>
+        <v>45888.80381288195</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | The New Sa</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>The New Saints – Connah's QuayCymru Premier</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2,80%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+25,9%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45888.85031668672</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 13.5 - tirs2e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fenerbahce – BenficaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+24,1%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45888.85031668672</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Larne FC –</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Larne FC – PortadownNIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2,70%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+8,16%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45888.85031668672</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | L.Jeanjean</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>L.Jeanjean – E.CocciarettoWTA - Monterrey</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>19/08 23:50</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+7,01%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45888.85031668672</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4246,10 +4246,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F89" t="n">
+        <v>45</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4262,7 +4260,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45888.85031668672</v>
+        <v>45888.85031668982</v>
       </c>
     </row>
     <row r="90">
@@ -4291,10 +4289,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F90" t="n">
+        <v>2.7</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4307,7 +4303,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45888.85031668672</v>
+        <v>45888.85031668982</v>
       </c>
     </row>
     <row r="91">
@@ -4336,10 +4332,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F91" t="n">
+        <v>40</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4352,7 +4346,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>45888.85031668672</v>
+        <v>45888.85031668982</v>
       </c>
     </row>
     <row r="92">
@@ -4381,10 +4375,8 @@
           <t>19/08 23:50</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F92" t="n">
+        <v>6</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4397,7 +4389,322 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45888.85031668672</v>
+        <v>45888.85031668982</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs2e équipe | Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fenerbahçe – BenficaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>20/08 19:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>+23,3%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Paris SG –</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Paris SG – AngersLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>22/08 18:45</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Gaziantep </t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Gaziantep FK – GenclerbirligiSüper Lig</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fenerbahce – KocaelisporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>+9,25%</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Golden State ValkyriesUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>20/08 02:00</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>+8,60%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 9.5 - tir cadré | Sao Paulo </t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sao Paulo SP – Atletico NacionalInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>20/08 00:30</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>+8,40%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>45888.9308462124</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Sportivo AmelianoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>+7,30%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>45888.9308462124</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-19.xlsx
+++ b/data/valuebets_database_2025-08-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4418,10 +4418,8 @@
           <t>20/08 19:00</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F93" t="n">
+        <v>2.8</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4434,7 +4432,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="94">
@@ -4463,10 +4461,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F94" t="n">
+        <v>2.5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4479,7 +4475,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="95">
@@ -4508,10 +4504,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F95" t="n">
+        <v>50</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4524,7 +4518,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="96">
@@ -4553,10 +4547,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F96" t="n">
+        <v>50</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4569,7 +4561,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="97">
@@ -4598,10 +4590,8 @@
           <t>20/08 02:00</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F97" t="n">
+        <v>19</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4614,7 +4604,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="98">
@@ -4643,10 +4633,8 @@
           <t>20/08 00:30</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F98" t="n">
+        <v>3.6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4659,7 +4647,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
       </c>
     </row>
     <row r="99">
@@ -4688,10 +4676,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F99" t="n">
+        <v>40</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4704,7 +4690,187 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45888.9308462124</v>
+        <v>45888.93084621528</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | H 2 (+1.5)P | République</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>République Dominicaine – ColombieInternational - Americup</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>H 2 (+1.5)P</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>23/08 03:10</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>45888.97220652205</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 11-2 | C.Harrison</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>C.Harrison / D.Collins – A.Vavassori / S.ErraniATP - US Open, Doubles Mixte</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>20/08 23:00</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>+9,41%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>45888.97220652205</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 21-21er set | Scott Jone</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Scott Jones – Rohan Hazratwala385076e7 UTR Men - Gold Coast</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>21-21er set</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>20/08 02:10</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>11.50</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>+8,39%</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>45888.97220652205</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | H 1 (+9.5)P | Panama – P</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Panama – Porto-RicoInternational - Americup</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>H 1 (+9.5)P</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>22/08 19:10</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>+6,73%</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>45888.97220652205</v>
       </c>
     </row>
   </sheetData>
